--- a/product_selector_out/STM32WL series.xlsx
+++ b/product_selector_out/STM32WL series.xlsx
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl3rk8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl30k8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="BP28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="BP29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="BP30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="BP31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="BP32" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="BP33" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="BP35" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="BP36" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="BP37" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="BP38" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="BP39" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="BP40" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11268,7 @@
       </c>
       <c r="BP41" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12609,9 +12609,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -12924,9 +12924,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12951,9 +12951,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -13266,9 +13266,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13635,9 +13635,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -13950,9 +13950,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13977,9 +13977,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -14292,9 +14292,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14319,9 +14319,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -14634,9 +14634,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14661,9 +14661,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -14976,9 +14976,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15345,9 +15345,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -15660,9 +15660,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15687,9 +15687,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -16002,9 +16002,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16029,9 +16029,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -16344,9 +16344,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16713,9 +16713,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -17028,9 +17028,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17397,9 +17397,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -17622,14 +17622,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ27" s="6" t="inlineStr">
@@ -17712,9 +17712,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17739,9 +17739,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -17964,14 +17964,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ28" s="6" t="inlineStr">
@@ -18054,9 +18054,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -18081,9 +18081,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -18306,14 +18306,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ29" s="6" t="inlineStr">
@@ -18396,9 +18396,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -18423,9 +18423,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -18648,14 +18648,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ30" s="6" t="inlineStr">
@@ -18738,9 +18738,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -18765,9 +18765,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -18990,14 +18990,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ31" s="6" t="inlineStr">
@@ -19080,9 +19080,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -19107,9 +19107,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -19332,14 +19332,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ32" s="6" t="inlineStr">
@@ -19422,9 +19422,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -19449,9 +19449,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -19674,14 +19674,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ33" s="6" t="inlineStr">
@@ -19764,9 +19764,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20133,9 +20133,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -20358,14 +20358,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ35" s="6" t="inlineStr">
@@ -20448,9 +20448,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20475,9 +20475,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -20700,14 +20700,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ36" s="6" t="inlineStr">
@@ -20790,9 +20790,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20817,9 +20817,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -21042,14 +21042,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ37" s="6" t="inlineStr">
@@ -21132,9 +21132,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21159,9 +21159,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -21384,14 +21384,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ38" s="6" t="inlineStr">
@@ -21474,9 +21474,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21501,9 +21501,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -21726,14 +21726,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ39" s="6" t="inlineStr">
@@ -21816,9 +21816,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21843,9 +21843,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -22068,14 +22068,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ40" s="6" t="inlineStr">
@@ -22158,9 +22158,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -22185,9 +22185,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -22410,14 +22410,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ41" s="6" t="inlineStr">
@@ -22500,9 +22500,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22919,7 +22919,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WL54CC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -22941,7 +22941,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WL54CC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -22956,14 +22956,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32WLE4C8</t>
+          <t>STM32WLE5C8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -22978,381 +22978,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32WLE5JB</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32WL54JC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32WL54JC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32WLE5CC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32WLE5JC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32WL55JC</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32WL55JC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32WL55CC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32WL55CC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32WLE5J8</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32WLE4J8</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32WLE4JB</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32WLE4CB</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32WLE4CC</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32WLE4JC</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32WLE5CB</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32WLE5C8</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32WL series.xlsx
+++ b/product_selector_out/STM32WL series.xlsx
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl3rk8.pdf</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl30k8.pdf</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="BP28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="BP29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="BP30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="BP31" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="BP32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="BP33" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="BP35" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="BP36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="BP37" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="BP38" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="BP39" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="BP40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11268,7 @@
       </c>
       <c r="BP41" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -12609,9 +12609,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -12924,9 +12924,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -12951,9 +12951,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -13266,9 +13266,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13635,9 +13635,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -13950,9 +13950,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13977,9 +13977,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -14292,9 +14292,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -14319,9 +14319,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -14634,9 +14634,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -14661,9 +14661,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -14976,9 +14976,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -15345,9 +15345,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -15660,9 +15660,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -15687,9 +15687,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -16002,9 +16002,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -16029,9 +16029,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -16344,9 +16344,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -16713,9 +16713,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -17028,9 +17028,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -17397,9 +17397,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -17622,14 +17622,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ27" s="6" t="inlineStr">
@@ -17712,9 +17712,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -17739,9 +17739,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -17964,14 +17964,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ28" s="6" t="inlineStr">
@@ -18054,9 +18054,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -18081,9 +18081,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -18306,14 +18306,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ29" s="6" t="inlineStr">
@@ -18396,9 +18396,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -18423,9 +18423,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -18648,14 +18648,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ30" s="6" t="inlineStr">
@@ -18738,9 +18738,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP30" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -18765,9 +18765,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -18990,14 +18990,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ31" s="6" t="inlineStr">
@@ -19080,9 +19080,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP31" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -19107,9 +19107,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -19332,14 +19332,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ32" s="6" t="inlineStr">
@@ -19422,9 +19422,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP32" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -19449,9 +19449,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -19674,14 +19674,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ33" s="6" t="inlineStr">
@@ -19764,9 +19764,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP33" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -20133,9 +20133,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -20358,14 +20358,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ35" s="6" t="inlineStr">
@@ -20448,9 +20448,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP35" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -20475,9 +20475,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -20700,14 +20700,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ36" s="6" t="inlineStr">
@@ -20790,9 +20790,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP36" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -20817,9 +20817,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -21042,14 +21042,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ37" s="6" t="inlineStr">
@@ -21132,9 +21132,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP37" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -21159,9 +21159,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -21384,14 +21384,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ38" s="6" t="inlineStr">
@@ -21474,9 +21474,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP38" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -21501,9 +21501,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -21726,14 +21726,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ39" s="6" t="inlineStr">
@@ -21816,9 +21816,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP39" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -21843,9 +21843,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -22068,14 +22068,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ40" s="6" t="inlineStr">
@@ -22158,9 +22158,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP40" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -22185,9 +22185,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -22410,14 +22410,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ41" s="6" t="inlineStr">
@@ -22500,9 +22500,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP41" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22919,7 +22919,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WL55CC</t>
+          <t>STM32WL54CC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -22941,7 +22941,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WL55CC</t>
+          <t>STM32WL54CC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -22963,20 +22963,394 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>STM32WLE4C8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32WLE5JB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32WL54JC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32WL54JC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32WLE5CC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32WLE5JC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32WL55JC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32WL55JC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32WL55CC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32WL55CC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32WLE5J8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32WLE4J8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32WLE4JB</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32WLE4CB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32WLE4CC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32WLE4JC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32WLE5CB</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>STM32WLE5C8</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32WL series.xlsx
+++ b/product_selector_out/STM32WL series.xlsx
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl3rk8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl30k8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="BP28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="BP29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="BP30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="BP31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="BP32" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="BP33" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="BP35" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="BP36" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="BP37" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="BP38" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="BP39" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="BP40" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11268,7 @@
       </c>
       <c r="BP41" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12609,9 +12609,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -12924,9 +12924,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12951,9 +12951,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -13266,9 +13266,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13635,9 +13635,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -13950,9 +13950,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13977,9 +13977,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -14292,9 +14292,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14319,9 +14319,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -14634,9 +14634,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14661,9 +14661,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -14976,9 +14976,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15345,9 +15345,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -15660,9 +15660,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15687,9 +15687,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -16002,9 +16002,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16029,9 +16029,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -16344,9 +16344,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16713,9 +16713,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -17028,9 +17028,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17397,9 +17397,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -17622,14 +17622,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ27" s="6" t="inlineStr">
@@ -17712,9 +17712,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17739,9 +17739,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -17964,14 +17964,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ28" s="6" t="inlineStr">
@@ -18054,9 +18054,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -18081,9 +18081,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -18306,14 +18306,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ29" s="6" t="inlineStr">
@@ -18396,9 +18396,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -18423,9 +18423,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -18648,14 +18648,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ30" s="6" t="inlineStr">
@@ -18738,9 +18738,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -18765,9 +18765,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -18990,14 +18990,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ31" s="6" t="inlineStr">
@@ -19080,9 +19080,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -19107,9 +19107,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -19332,14 +19332,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ32" s="6" t="inlineStr">
@@ -19422,9 +19422,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -19449,9 +19449,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -19674,14 +19674,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ33" s="6" t="inlineStr">
@@ -19764,9 +19764,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20133,9 +20133,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -20358,14 +20358,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ35" s="6" t="inlineStr">
@@ -20448,9 +20448,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20475,9 +20475,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -20700,14 +20700,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ36" s="6" t="inlineStr">
@@ -20790,9 +20790,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20817,9 +20817,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -21042,14 +21042,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ37" s="6" t="inlineStr">
@@ -21132,9 +21132,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21159,9 +21159,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -21384,14 +21384,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ38" s="6" t="inlineStr">
@@ -21474,9 +21474,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21501,9 +21501,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -21726,14 +21726,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ39" s="6" t="inlineStr">
@@ -21816,9 +21816,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21843,9 +21843,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -22068,14 +22068,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ40" s="6" t="inlineStr">
@@ -22158,9 +22158,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -22185,9 +22185,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -22410,14 +22410,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ41" s="6" t="inlineStr">
@@ -22500,9 +22500,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22919,7 +22919,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WL54CC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -22941,7 +22941,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WL54CC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -22963,7 +22963,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32WLE4C8</t>
+          <t>STM32WLE5C8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -22977,380 +22977,6 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32WLE5JB</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32WL54JC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32WL54JC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32WLE5CC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32WLE5JC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32WL55JC</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32WL55JC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32WL55CC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32WL55CC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32WLE5J8</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32WLE4J8</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32WLE4JB</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32WLE4CB</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32WLE4CC</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32WLE4JC</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32WLE5CB</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32WLE5C8</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
         <is>
           <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32WL series.xlsx
+++ b/product_selector_out/STM32WL series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP42"/>
+  <dimension ref="A1:BQ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.43359375" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,8 @@
     <col width="21.984375" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
     <col width="18" customWidth="1" min="67" max="67"/>
-    <col width="52" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="68" max="68"/>
+    <col width="52" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1011,6 +1017,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1350,6 +1357,11 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl3rk8.pdf</t>
         </is>
       </c>
@@ -1695,6 +1707,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2037,6 +2054,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2376,6 +2398,11 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
@@ -2721,6 +2748,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3063,6 +3095,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3405,6 +3442,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3747,6 +3789,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4086,6 +4133,11 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
         </is>
       </c>
@@ -4431,6 +4483,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4773,6 +4830,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5115,6 +5177,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5454,6 +5521,11 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl30k8.pdf</t>
         </is>
       </c>
@@ -5799,6 +5871,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -6138,6 +6215,11 @@
       </c>
       <c r="BP26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl5moc.pdf</t>
         </is>
       </c>
@@ -6483,6 +6565,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -6825,6 +6912,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -7167,6 +7259,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -7509,6 +7606,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ30" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -7851,6 +7953,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ31" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -8193,6 +8300,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -8535,6 +8647,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ33" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -8874,6 +8991,11 @@
       </c>
       <c r="BP34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
         </is>
       </c>
@@ -9219,6 +9341,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -9561,6 +9688,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ36" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -9903,6 +10035,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -10245,6 +10382,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -10587,6 +10729,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -10929,6 +11076,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ40" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -11271,6 +11423,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -11610,12 +11767,17 @@
       </c>
       <c r="BP42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -11638,14 +11800,13 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -11663,6 +11824,7 @@
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A9:BQ9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
     <mergeCell ref="K10:K11"/>
@@ -11675,6 +11837,7 @@
     <mergeCell ref="AX10:AX11"/>
     <mergeCell ref="AZ10:AZ11"/>
     <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="BO10:BO11"/>
@@ -11728,7 +11891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP42"/>
+  <dimension ref="A1:BQ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11799,6 +11962,7 @@
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
     <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12147,6 +12311,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -12245,6 +12414,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -12582,7 +12752,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
+      <c r="BP12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12929,6 +13104,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -13271,6 +13451,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -13608,7 +13793,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
+      <c r="BP15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13955,6 +14145,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -14297,6 +14492,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -14639,6 +14839,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -14981,6 +15186,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -15318,7 +15528,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
+      <c r="BP20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15665,6 +15880,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -16007,6 +16227,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -16349,6 +16574,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -16686,7 +16916,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
+      <c r="BP24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17033,6 +17268,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -17370,7 +17610,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP26" s="6" t="inlineStr">
+      <c r="BP26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17717,6 +17962,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -18059,6 +18309,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -18401,6 +18656,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -18743,6 +19003,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -19085,6 +19350,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -19427,6 +19697,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -19769,6 +20044,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -20106,7 +20386,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP34" s="6" t="inlineStr">
+      <c r="BP34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20453,6 +20738,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -20795,6 +21085,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -21137,6 +21432,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -21479,6 +21779,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -21821,6 +22126,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -22163,6 +22473,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -22505,6 +22820,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -22842,7 +23162,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP42" s="6" t="inlineStr">
+      <c r="BP42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22850,8 +23175,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BP8"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
+    <mergeCell ref="A9:BQ9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
